--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487202_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487202_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9431</v>
+        <v>8.6173</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2082</v>
+        <v>8.6683</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2652</v>
+        <v>-0.051</v>
       </c>
       <c r="G2" t="n">
         <v>6.7769</v>
@@ -610,13 +610,13 @@
         <v>2.5091</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9267</v>
+        <v>-0.2525</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3886</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5381</v>
+        <v>-0.3239</v>
       </c>
       <c r="V2" t="n">
         <v>1.5138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5166</v>
+        <v>3.7893</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1429</v>
+        <v>4.6029</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6263</v>
+        <v>-0.8137</v>
       </c>
       <c r="G3" t="n">
         <v>1.6549</v>
@@ -688,13 +688,13 @@
         <v>2.8951</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5546</v>
+        <v>-0.2819</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3886</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1659</v>
+        <v>-0.3533</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2859</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3802</v>
+        <v>0.3524</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0837</v>
+        <v>0.2433</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2965</v>
+        <v>0.1091</v>
       </c>
       <c r="G4" t="n">
         <v>-1.5049</v>
@@ -766,13 +766,13 @@
         <v>3.2811</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.08</v>
+        <v>-0.1077</v>
       </c>
       <c r="T4" t="n">
-        <v>0.041</v>
+        <v>0.2007</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.121</v>
+        <v>-0.3084</v>
       </c>
       <c r="V4" t="n">
         <v>0.614</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3218</v>
+        <v>-1.1069</v>
       </c>
       <c r="E5" t="n">
-        <v>1.248</v>
+        <v>-0.154</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9262</v>
+        <v>-0.9529</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7152</v>
@@ -844,13 +844,13 @@
         <v>0.965</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2071</v>
+        <v>0.7783</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1496</v>
+        <v>0.7476</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0575</v>
+        <v>0.0307</v>
       </c>
       <c r="V5" t="n">
         <v>-0.9421</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3983</v>
+        <v>-1.9549</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3574</v>
+        <v>-1.6999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0409</v>
+        <v>-0.255</v>
       </c>
       <c r="G6" t="n">
         <v>-1.1568</v>
@@ -922,13 +922,13 @@
         <v>3.0881</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8309</v>
+        <v>0.2743</v>
       </c>
       <c r="T6" t="n">
-        <v>2.1628</v>
+        <v>0.8203</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3319</v>
+        <v>-0.546</v>
       </c>
       <c r="V6" t="n">
         <v>0.8576</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1391</v>
+        <v>-2.1054</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.833</v>
+        <v>-2.9332</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6939</v>
+        <v>0.8278</v>
       </c>
       <c r="G7" t="n">
         <v>-2.034</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2809</v>
+        <v>0.3146</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2657</v>
+        <v>0.1656</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0152</v>
+        <v>0.149</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. MARCOS SÁNCHEZ</t>
+          <t>D. BARROSO VALVERDE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,37 +1033,37 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7441</v>
+        <v>-2.6776</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2809</v>
+        <v>-2.5272</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4632</v>
+        <v>-0.1504</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1023</v>
+        <v>-1.9346</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6271</v>
+        <v>-1.1271</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4752</v>
+        <v>-0.8076</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3145</v>
+        <v>-1.2938</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0207</v>
+        <v>-0.6262</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3352</v>
+        <v>-0.6676</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.6408</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6478</v>
+        <v>-0.5009</v>
       </c>
       <c r="O8" t="n">
         <v>-0.14</v>
@@ -1078,13 +1078,13 @@
         <v>0.579</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1302</v>
+        <v>0.0291</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3847</v>
+        <v>0.1177</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2545</v>
+        <v>-0.0886</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BARROSO VALVERDE</t>
+          <t>A. MARCOS SÁNCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,37 +1111,37 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1852</v>
+        <v>-2.871</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9278</v>
+        <v>-2.381</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2575</v>
+        <v>-0.49</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9346</v>
+        <v>-2.1023</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1271</v>
+        <v>-0.6271</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8076</v>
+        <v>-1.4752</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2938</v>
+        <v>-1.3145</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6262</v>
+        <v>0.0207</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6676</v>
+        <v>-1.3352</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6408</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5009</v>
+        <v>-0.6478</v>
       </c>
       <c r="O9" t="n">
         <v>-0.14</v>
@@ -1156,13 +1156,13 @@
         <v>0.579</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4785</v>
+        <v>0.0033</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2829</v>
+        <v>0.2846</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1957</v>
+        <v>-0.2813</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9546</v>
+        <v>-3.1872</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4812</v>
+        <v>-3.5799</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5266</v>
+        <v>0.3927</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3125</v>
@@ -1234,13 +1234,13 @@
         <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7423</v>
+        <v>0.0251</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7588</v>
+        <v>0.1425</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0165</v>
+        <v>-0.1173</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2859</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4778</v>
+        <v>-3.296</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3954</v>
+        <v>-2.5348</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0824</v>
+        <v>-0.7611</v>
       </c>
       <c r="G11" t="n">
         <v>-4.155</v>
@@ -1312,13 +1312,13 @@
         <v>2.8951</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7463</v>
+        <v>-0.5645</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0562</v>
+        <v>-0.1956</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6901</v>
+        <v>-0.3689</v>
       </c>
       <c r="V11" t="n">
         <v>-1.4716</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7374</v>
+        <v>-4.44</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.592900000000002</v>
+        <v>-2.2955</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1447</v>
+        <v>-2.1445</v>
       </c>
       <c r="G12" t="n">
         <v>-9.483499999999999</v>
@@ -1390,10 +1390,10 @@
         <v>19.3006</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.07929999999999993</v>
+        <v>0.2181</v>
       </c>
       <c r="T12" t="n">
-        <v>2.128699999999999</v>
+        <v>2.4262</v>
       </c>
       <c r="U12" t="n">
         <v>-2.208</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5941</v>
+        <v>6.2131</v>
       </c>
       <c r="E13" t="n">
-        <v>3.174</v>
+        <v>2.8736</v>
       </c>
       <c r="F13" t="n">
-        <v>3.4201</v>
+        <v>3.3395</v>
       </c>
       <c r="G13" t="n">
         <v>2.5326</v>
@@ -1468,13 +1468,13 @@
         <v>1.5441</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8685</v>
+        <v>0.4875</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7694</v>
+        <v>0.469</v>
       </c>
       <c r="U13" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.0185</v>
       </c>
       <c r="V13" t="n">
         <v>1.842</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6236</v>
+        <v>3.0377</v>
       </c>
       <c r="E14" t="n">
-        <v>0.6128</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0109</v>
+        <v>2.2247</v>
       </c>
       <c r="G14" t="n">
         <v>1.004</v>
@@ -1546,13 +1546,13 @@
         <v>0.965</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2875</v>
+        <v>0.1266</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0304</v>
+        <v>0.1699</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2571</v>
+        <v>-0.0433</v>
       </c>
       <c r="V14" t="n">
         <v>0.9421</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. REINER</t>
+          <t>P. FERNANDEZ BLANCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8519</v>
+        <v>1.403</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2451</v>
+        <v>2.1207</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6067</v>
+        <v>-0.7176</v>
       </c>
       <c r="G15" t="n">
-        <v>1.3873</v>
+        <v>0.5831</v>
       </c>
       <c r="H15" t="n">
-        <v>2.3577</v>
+        <v>-0.3787</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9704</v>
+        <v>0.9618</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5553</v>
+        <v>2.579</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9069</v>
+        <v>1.4644</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3516</v>
+        <v>1.1146</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.168</v>
+        <v>-1.996</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5493</v>
+        <v>-1.8431</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3813</v>
+        <v>-0.1528</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="R15" t="n">
         <v>1.5441</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7211</v>
+        <v>-0.5311</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9518</v>
+        <v>-0.2654</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2307</v>
+        <v>-0.2657</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5717</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. YAILO</t>
+          <t>J. REINER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7276</v>
+        <v>0.9719</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.4454</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1751</v>
+        <v>0.5264</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3973</v>
+        <v>1.3873</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9285</v>
+        <v>2.3577</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5312</v>
+        <v>-0.9704</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9439</v>
+        <v>2.5553</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7811</v>
+        <v>3.9069</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1628</v>
+        <v>-1.3516</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3412</v>
+        <v>-1.168</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7096</v>
+        <v>-1.5493</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3684</v>
+        <v>0.3813</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.386</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.9301</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-4.0532</v>
-      </c>
       <c r="R16" t="n">
-        <v>2.1231</v>
+        <v>1.5441</v>
       </c>
       <c r="S16" t="n">
-        <v>1.827</v>
+        <v>-0.6012</v>
       </c>
       <c r="T16" t="n">
-        <v>1.556</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>0.271</v>
+        <v>0.1504</v>
       </c>
       <c r="V16" t="n">
-        <v>1.228</v>
+        <v>0.5717</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4559</v>
+        <v>0.5717</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. FERNANDEZ BLANCO</t>
+          <t>D. IBARLUCEA LAVIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6479</v>
+        <v>0.0621</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8202</v>
+        <v>1.5455</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1724</v>
+        <v>-1.4833</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5831</v>
+        <v>1.0126</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3787</v>
+        <v>0.3043</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9618</v>
+        <v>0.7083</v>
       </c>
       <c r="J17" t="n">
-        <v>2.579</v>
+        <v>2.0068</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4644</v>
+        <v>0.7452</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1146</v>
+        <v>1.2617</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.996</v>
+        <v>-0.9942</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8431</v>
+        <v>-0.4408</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1528</v>
+        <v>-0.5534</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3511</v>
+        <v>-0.965</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.193</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5441</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2863</v>
+        <v>0.0145</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5658</v>
+        <v>0.5037</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7205</v>
+        <v>-0.4891</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. IBARLUCEA LAVIN</t>
+          <t>A. YAILO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7125</v>
+        <v>-0.3079</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1449</v>
+        <v>0.0014</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8575</v>
+        <v>-0.3093</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0126</v>
+        <v>-0.3973</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3043</v>
+        <v>-0.9285</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7083</v>
+        <v>0.5312</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0068</v>
+        <v>0.9439</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7452</v>
+        <v>0.7811</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2617</v>
+        <v>0.1628</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9942</v>
+        <v>-1.3412</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4408</v>
+        <v>-1.7096</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5534</v>
+        <v>0.3684</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.965</v>
+        <v>-4.0532</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.1231</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7601</v>
+        <v>0.7915</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1031</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8633</v>
+        <v>0.1368</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4559</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. DE LA LLAMA RUIZ</t>
+          <t>L. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0567</v>
+        <v>-0.661</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9247</v>
+        <v>0.3147</v>
       </c>
       <c r="F20" t="n">
-        <v>1.868</v>
+        <v>-0.9757</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2924</v>
+        <v>3.1999</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3113</v>
+        <v>3.0157</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.0189</v>
+        <v>0.1842</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2196</v>
+        <v>3.6595</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4734</v>
+        <v>3.5703</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2538</v>
+        <v>0.0893</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9272</v>
+        <v>-0.4596</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1621</v>
+        <v>-0.5546</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2349</v>
+        <v>0.0949</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.7371</v>
+        <v>-2.7021</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.8602</v>
+        <v>-4.0532</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1231</v>
+        <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>0.388</v>
+        <v>0.6831</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2842</v>
+        <v>1.0365</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6722</v>
+        <v>-0.3533</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.842</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.3281</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. GOMEZ FERNANDEZ</t>
+          <t>B. DE LA LLAMA RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3813</v>
+        <v>-1.3581</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5941</v>
+        <v>-2.8246</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7873</v>
+        <v>1.4665</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.973</v>
+        <v>0.2924</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0673</v>
+        <v>1.3113</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0403</v>
+        <v>-1.0189</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1922</v>
+        <v>1.2196</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4347</v>
+        <v>2.4734</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6269</v>
+        <v>-1.2538</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7808</v>
+        <v>-0.9272</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3674</v>
+        <v>-1.1621</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4134</v>
+        <v>0.2349</v>
       </c>
       <c r="P21" t="n">
-        <v>0.965</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R21" t="n">
-        <v>0.965</v>
+        <v>2.1231</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1454</v>
+        <v>0.0866</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4019</v>
+        <v>-0.1841</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2564</v>
+        <v>0.2706</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. GOMEZ FERNANDEZ</t>
+          <t>A. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3831</v>
+        <v>-1.3883</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3147</v>
+        <v>-0.4939</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6979</v>
+        <v>-0.8943</v>
       </c>
       <c r="G22" t="n">
-        <v>3.1999</v>
+        <v>-0.973</v>
       </c>
       <c r="H22" t="n">
-        <v>3.0157</v>
+        <v>0.0673</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1842</v>
+        <v>-1.0403</v>
       </c>
       <c r="J22" t="n">
-        <v>3.6595</v>
+        <v>-0.1922</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5703</v>
+        <v>0.4347</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0893</v>
+        <v>-0.6269</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4596</v>
+        <v>-0.7808</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5546</v>
+        <v>-0.3674</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0949</v>
+        <v>-0.4134</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.7021</v>
+        <v>0.965</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.0532</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.039</v>
+        <v>-0.1524</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0365</v>
+        <v>-0.3017</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.0755</v>
+        <v>0.1494</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.842</v>
+        <v>-1.228</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.3281</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.5138</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1721</v>
+        <v>-1.8981</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.0645</v>
+        <v>-1.1646</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1076</v>
+        <v>-0.7335</v>
       </c>
       <c r="G23" t="n">
         <v>0.636</v>
@@ -2248,13 +2248,13 @@
         <v>1.3511</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4429</v>
+        <v>0.7168</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2149</v>
+        <v>1.1148</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7721</v>
+        <v>-0.3979</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5138</v>
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>4.7376</v>
+        <v>6.0726</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8007</v>
+        <v>2.8008</v>
       </c>
       <c r="F24" t="n">
-        <v>1.936500000000001</v>
+        <v>3.271999999999998</v>
       </c>
       <c r="G24" t="n">
-        <v>9.4834</v>
+        <v>9.483399999999998</v>
       </c>
       <c r="H24" t="n">
         <v>6.877299999999999</v>
@@ -2317,7 +2317,7 @@
         <v>3.113</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.825200000000001</v>
+        <v>-4.8252</v>
       </c>
       <c r="Q24" t="n">
         <v>-19.3008</v>
@@ -2326,16 +2326,16 @@
         <v>14.4757</v>
       </c>
       <c r="S24" t="n">
-        <v>0.07940000000000003</v>
+        <v>1.4143</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2078</v>
+        <v>2.2079</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.1287</v>
+        <v>-0.7931999999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-4.440892098500626e-16</v>
       </c>
       <c r="W24" t="n">
         <v>5.4413</v>
